--- a/acceuil-version2/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/acceuil-version2/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:26:49+00:00</t>
+    <t>2026-06-16T12:27:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/acceuil-version2/ig/CdaSTEDONToStringConceptMap.xlsx
+++ b/acceuil-version2/ig/CdaSTEDONToStringConceptMap.xlsx
@@ -62,7 +62,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T12:27:53+00:00</t>
+    <t>2026-06-16T12:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
